--- a/test-data/dane-syntetyczne-with-errors.xlsx
+++ b/test-data/dane-syntetyczne-with-errors.xlsx
@@ -4040,7 +4040,7 @@
       <c r="E81">
         <v>30207.36</v>
       </c>
-      <c r="G81">
+      <c r="F81">
         <v>1</v>
       </c>
       <c r="M81">
@@ -6339,7 +6339,7 @@
       <c r="E137">
         <v>30844.2</v>
       </c>
-      <c r="G137">
+      <c r="F137">
         <v>1</v>
       </c>
       <c r="N137">
@@ -8465,7 +8465,7 @@
       <c r="E186">
         <v>11997.6</v>
       </c>
-      <c r="G186">
+      <c r="F186">
         <v>1</v>
       </c>
       <c r="P186">
@@ -9826,7 +9826,7 @@
       <c r="E217">
         <v>28286</v>
       </c>
-      <c r="G217">
+      <c r="F217">
         <v>1</v>
       </c>
       <c r="Q217">
@@ -10560,7 +10560,7 @@
       <c r="E233">
         <v>34337.71</v>
       </c>
-      <c r="G233">
+      <c r="F233">
         <v>1</v>
       </c>
       <c r="R233">
@@ -13254,7 +13254,7 @@
       <c r="E296">
         <v>11798.16</v>
       </c>
-      <c r="G296">
+      <c r="F296">
         <v>1</v>
       </c>
       <c r="T296">
@@ -13689,7 +13689,7 @@
       <c r="E305">
         <v>37076.16</v>
       </c>
-      <c r="G305">
+      <c r="F305">
         <v>1</v>
       </c>
       <c r="T305">
@@ -13997,7 +13997,7 @@
       <c r="E312">
         <v>14418.8</v>
       </c>
-      <c r="G312">
+      <c r="F312">
         <v>1</v>
       </c>
       <c r="T312">
@@ -15600,7 +15600,7 @@
       <c r="E347">
         <v>75619.92</v>
       </c>
-      <c r="G347">
+      <c r="F347">
         <v>1</v>
       </c>
       <c r="U347">
@@ -17055,7 +17055,7 @@
       <c r="E377">
         <v>25770.36</v>
       </c>
-      <c r="G377">
+      <c r="F377">
         <v>1</v>
       </c>
       <c r="V377">
@@ -17167,7 +17167,7 @@
       <c r="E379">
         <v>30909.84</v>
       </c>
-      <c r="G379">
+      <c r="F379">
         <v>1</v>
       </c>
       <c r="V379">
@@ -19844,7 +19844,7 @@
       <c r="E441">
         <v>76224.72</v>
       </c>
-      <c r="G441">
+      <c r="F441">
         <v>1</v>
       </c>
       <c r="X441">
@@ -20588,7 +20588,7 @@
       <c r="E456">
         <v>16712.16</v>
       </c>
-      <c r="G456">
+      <c r="F456">
         <v>1</v>
       </c>
       <c r="X456">
@@ -21852,7 +21852,7 @@
       <c r="E482">
         <v>11340.12</v>
       </c>
-      <c r="G482">
+      <c r="F482">
         <v>1</v>
       </c>
       <c r="Y482">
@@ -24767,7 +24767,7 @@
       <c r="E543">
         <v>13118.88</v>
       </c>
-      <c r="G543">
+      <c r="F543">
         <v>1</v>
       </c>
       <c r="Z543">
@@ -26098,7 +26098,7 @@
       <c r="E574">
         <v>30489.24</v>
       </c>
-      <c r="G574">
+      <c r="F574">
         <v>1</v>
       </c>
       <c r="AA574">
@@ -26539,7 +26539,7 @@
       <c r="E583">
         <v>35256.48</v>
       </c>
-      <c r="G583">
+      <c r="F583">
         <v>1</v>
       </c>
       <c r="AA583">
@@ -27377,7 +27377,7 @@
       <c r="E600">
         <v>34885.56</v>
       </c>
-      <c r="G600">
+      <c r="F600">
         <v>1</v>
       </c>
       <c r="AB600">
@@ -32158,7 +32158,7 @@
       <c r="E703">
         <v>10756.56</v>
       </c>
-      <c r="G703">
+      <c r="F703">
         <v>1</v>
       </c>
       <c r="AD703">
@@ -32959,7 +32959,7 @@
       <c r="E718">
         <v>15381.24</v>
       </c>
-      <c r="G718">
+      <c r="F718">
         <v>1</v>
       </c>
       <c r="AD718">
@@ -34010,7 +34010,7 @@
       <c r="E741">
         <v>25616.88</v>
       </c>
-      <c r="G741">
+      <c r="F741">
         <v>1</v>
       </c>
       <c r="AE741">
@@ -38238,7 +38238,7 @@
       <c r="E830">
         <v>32075.28</v>
       </c>
-      <c r="G830">
+      <c r="F830">
         <v>1</v>
       </c>
       <c r="AG830">
@@ -38350,7 +38350,7 @@
       <c r="E832">
         <v>26229.6</v>
       </c>
-      <c r="G832">
+      <c r="F832">
         <v>1</v>
       </c>
       <c r="AG832">
@@ -38534,7 +38534,7 @@
       <c r="E837">
         <v>44434.32</v>
       </c>
-      <c r="G837">
+      <c r="F837">
         <v>1</v>
       </c>
       <c r="AG837">
@@ -39585,7 +39585,7 @@
       <c r="E860">
         <v>12877.56</v>
       </c>
-      <c r="G860">
+      <c r="F860">
         <v>1</v>
       </c>
       <c r="AH860">
@@ -40123,7 +40123,7 @@
       <c r="E871">
         <v>27654.24</v>
       </c>
-      <c r="G871">
+      <c r="F871">
         <v>1</v>
       </c>
       <c r="AH871">
@@ -41418,7 +41418,7 @@
       <c r="E902">
         <v>89069.76</v>
       </c>
-      <c r="G902">
+      <c r="F902">
         <v>1</v>
       </c>
       <c r="AH902">
@@ -42735,7 +42735,7 @@
       <c r="E929">
         <v>12252.12</v>
       </c>
-      <c r="G929">
+      <c r="F929">
         <v>1</v>
       </c>
       <c r="AI929">
@@ -45209,7 +45209,7 @@
       <c r="E984">
         <v>29370.12</v>
       </c>
-      <c r="G984">
+      <c r="F984">
         <v>1</v>
       </c>
       <c r="AK984">
@@ -45288,7 +45288,7 @@
       <c r="E986">
         <v>43674.96</v>
       </c>
-      <c r="G986">
+      <c r="F986">
         <v>1</v>
       </c>
       <c r="AK986">
@@ -46520,7 +46520,7 @@
       <c r="E1014">
         <v>23784.6</v>
       </c>
-      <c r="G1014">
+      <c r="F1014">
         <v>1</v>
       </c>
       <c r="AK1014">

--- a/test-data/dane-syntetyczne-with-errors.xlsx
+++ b/test-data/dane-syntetyczne-with-errors.xlsx
@@ -1553,11 +1553,8 @@
       <c r="E27">
         <v>-38905.2</v>
       </c>
-      <c r="J27">
-        <v>-3242.1</v>
-      </c>
       <c r="K27">
-        <v>-3242.1</v>
+        <v>-6484.2</v>
       </c>
       <c r="L27">
         <v>-3242.1</v>
@@ -1606,7 +1603,7 @@
       <c r="E28">
         <v>-9583.19</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>-9583.19</v>
       </c>
     </row>
@@ -2638,7 +2635,7 @@
       <c r="E49">
         <v>-28327.57</v>
       </c>
-      <c r="K49">
+      <c r="L49">
         <v>-28327.57</v>
       </c>
     </row>
@@ -3802,11 +3799,8 @@
       <c r="E76">
         <v>-43766.88</v>
       </c>
-      <c r="L76">
-        <v>-3647.24</v>
-      </c>
       <c r="M76">
-        <v>-3647.24</v>
+        <v>-7294.48</v>
       </c>
       <c r="N76">
         <v>-3647.24</v>
@@ -3855,11 +3849,8 @@
       <c r="E77">
         <v>-15948.24</v>
       </c>
-      <c r="L77">
-        <v>-1329.02</v>
-      </c>
       <c r="M77">
-        <v>-1329.02</v>
+        <v>-2658.04</v>
       </c>
       <c r="N77">
         <v>-1329.02</v>
@@ -3908,14 +3899,8 @@
       <c r="E78">
         <v>-34014.24</v>
       </c>
-      <c r="K78">
-        <v>-2834.52</v>
-      </c>
-      <c r="L78">
-        <v>-2834.52</v>
-      </c>
       <c r="M78">
-        <v>-2834.52</v>
+        <v>-8503.56</v>
       </c>
       <c r="N78">
         <v>-2834.52</v>
@@ -4962,11 +4947,8 @@
       <c r="E104">
         <v>-25960.32</v>
       </c>
-      <c r="M104">
-        <v>-2163.36</v>
-      </c>
       <c r="N104">
-        <v>-2163.36</v>
+        <v>-4326.72</v>
       </c>
       <c r="O104">
         <v>-2163.36</v>
@@ -5015,14 +4997,8 @@
       <c r="E105">
         <v>-14400</v>
       </c>
-      <c r="L105">
-        <v>-1200</v>
-      </c>
-      <c r="M105">
-        <v>-1200</v>
-      </c>
       <c r="N105">
-        <v>-1200</v>
+        <v>-3600</v>
       </c>
       <c r="O105">
         <v>-1200</v>
@@ -5068,7 +5044,7 @@
       <c r="E106">
         <v>-8198.23</v>
       </c>
-      <c r="L106">
+      <c r="N106">
         <v>-8198.23</v>
       </c>
     </row>
@@ -7954,7 +7930,7 @@
       <c r="E175">
         <v>-18485.26</v>
       </c>
-      <c r="O175">
+      <c r="P175">
         <v>-18485.26</v>
       </c>
     </row>
@@ -9159,11 +9135,8 @@
       <c r="E200">
         <v>-3384.45</v>
       </c>
-      <c r="P200">
-        <v>-676.89</v>
-      </c>
       <c r="Q200">
-        <v>-676.89</v>
+        <v>-1353.78</v>
       </c>
       <c r="R200">
         <v>-676.89</v>
@@ -11438,14 +11411,8 @@
       <c r="E252">
         <v>-14023.44</v>
       </c>
-      <c r="Q252">
-        <v>-1168.62</v>
-      </c>
-      <c r="R252">
-        <v>-1168.62</v>
-      </c>
       <c r="S252">
-        <v>-1168.62</v>
+        <v>-3505.86</v>
       </c>
       <c r="T252">
         <v>-1168.62</v>
@@ -12798,11 +12765,8 @@
       <c r="E284">
         <v>-2839.5</v>
       </c>
-      <c r="S284">
-        <v>-473.25</v>
-      </c>
       <c r="T284">
-        <v>-473.25</v>
+        <v>-946.5</v>
       </c>
       <c r="U284">
         <v>-473.25</v>
@@ -14265,14 +14229,8 @@
       <c r="E317">
         <v>-9706.92</v>
       </c>
-      <c r="S317">
-        <v>-808.91</v>
-      </c>
-      <c r="T317">
-        <v>-808.91</v>
-      </c>
       <c r="U317">
-        <v>-808.91</v>
+        <v>-2426.73</v>
       </c>
       <c r="V317">
         <v>-808.91</v>
@@ -14318,11 +14276,8 @@
       <c r="E318">
         <v>-45267</v>
       </c>
-      <c r="T318">
-        <v>-3772.25</v>
-      </c>
       <c r="U318">
-        <v>-3772.25</v>
+        <v>-7544.5</v>
       </c>
       <c r="V318">
         <v>-3772.25</v>
@@ -16030,7 +15985,7 @@
       <c r="E355">
         <v>-7591.63</v>
       </c>
-      <c r="U355">
+      <c r="V355">
         <v>-7591.63</v>
       </c>
     </row>
@@ -16050,14 +16005,8 @@
       <c r="E356">
         <v>-2042.46</v>
       </c>
-      <c r="T356">
-        <v>-680.82</v>
-      </c>
-      <c r="U356">
-        <v>-680.82</v>
-      </c>
       <c r="V356">
-        <v>-680.82</v>
+        <v>-2042.46</v>
       </c>
     </row>
     <row r="357">
@@ -16076,11 +16025,8 @@
       <c r="E357">
         <v>-2748.48</v>
       </c>
-      <c r="U357">
-        <v>-343.56</v>
-      </c>
       <c r="V357">
-        <v>-343.56</v>
+        <v>-687.12</v>
       </c>
       <c r="W357">
         <v>-343.56</v>
@@ -17561,11 +17507,8 @@
       <c r="E387">
         <v>-34120.92</v>
       </c>
-      <c r="V387">
-        <v>-2843.41</v>
-      </c>
       <c r="W387">
-        <v>-2843.41</v>
+        <v>-5686.82</v>
       </c>
       <c r="X387">
         <v>-2843.41</v>
@@ -19284,14 +19227,8 @@
       <c r="E428">
         <v>-24965.88</v>
       </c>
-      <c r="V428">
-        <v>-2080.49</v>
-      </c>
-      <c r="W428">
-        <v>-2080.49</v>
-      </c>
       <c r="X428">
-        <v>-2080.49</v>
+        <v>-6241.47</v>
       </c>
       <c r="Y428">
         <v>-2080.49</v>
@@ -19337,14 +19274,8 @@
       <c r="E429">
         <v>-30909.84</v>
       </c>
-      <c r="V429">
-        <v>-2575.82</v>
-      </c>
-      <c r="W429">
-        <v>-2575.82</v>
-      </c>
       <c r="X429">
-        <v>-2575.82</v>
+        <v>-7727.46</v>
       </c>
       <c r="Y429">
         <v>-2575.82</v>
@@ -21013,7 +20944,7 @@
       <c r="E463">
         <v>-8140.97</v>
       </c>
-      <c r="W463">
+      <c r="Y463">
         <v>-8140.97</v>
       </c>
     </row>
@@ -22921,14 +22852,8 @@
       <c r="E505">
         <v>-2538.66</v>
       </c>
-      <c r="X505">
-        <v>-423.11</v>
-      </c>
-      <c r="Y505">
-        <v>-423.11</v>
-      </c>
       <c r="Z505">
-        <v>-423.11</v>
+        <v>-1269.33</v>
       </c>
       <c r="AA505">
         <v>-423.11</v>
@@ -22956,7 +22881,7 @@
       <c r="E506">
         <v>-17958.09</v>
       </c>
-      <c r="Y506">
+      <c r="Z506">
         <v>-17958.09</v>
       </c>
     </row>
@@ -24858,11 +24783,8 @@
       <c r="E545">
         <v>-20669.28</v>
       </c>
-      <c r="Z545">
-        <v>-1722.44</v>
-      </c>
       <c r="AA545">
-        <v>-1722.44</v>
+        <v>-3444.88</v>
       </c>
       <c r="AB545">
         <v>-1722.44</v>
@@ -29371,11 +29293,8 @@
       <c r="E643">
         <v>-835.28</v>
       </c>
-      <c r="AB643">
-        <v>-417.64</v>
-      </c>
       <c r="AC643">
-        <v>-417.64</v>
+        <v>-835.28</v>
       </c>
     </row>
     <row r="644">
@@ -29394,11 +29313,8 @@
       <c r="E644">
         <v>-18960.84</v>
       </c>
-      <c r="AB644">
-        <v>-1580.07</v>
-      </c>
       <c r="AC644">
-        <v>-1580.07</v>
+        <v>-3160.14</v>
       </c>
       <c r="AD644">
         <v>-1580.07</v>
@@ -29447,11 +29363,8 @@
       <c r="E645">
         <v>-646.47</v>
       </c>
-      <c r="AB645">
-        <v>-215.49</v>
-      </c>
       <c r="AC645">
-        <v>-215.49</v>
+        <v>-430.98</v>
       </c>
       <c r="AD645">
         <v>-215.49</v>
@@ -29473,11 +29386,8 @@
       <c r="E646">
         <v>-5223.9</v>
       </c>
-      <c r="AB646">
-        <v>-522.39</v>
-      </c>
       <c r="AC646">
-        <v>-522.39</v>
+        <v>-1044.78</v>
       </c>
       <c r="AD646">
         <v>-522.39</v>
@@ -29520,14 +29430,8 @@
       <c r="E647">
         <v>-23360.64</v>
       </c>
-      <c r="AA647">
-        <v>-1946.72</v>
-      </c>
-      <c r="AB647">
-        <v>-1946.72</v>
-      </c>
       <c r="AC647">
-        <v>-1946.72</v>
+        <v>-5840.16</v>
       </c>
       <c r="AD647">
         <v>-1946.72</v>
@@ -31656,7 +31560,7 @@
       <c r="E692">
         <v>-17170.66</v>
       </c>
-      <c r="AB692">
+      <c r="AD692">
         <v>-17170.66</v>
       </c>
     </row>
@@ -31676,11 +31580,8 @@
       <c r="E693">
         <v>-77718.24</v>
       </c>
-      <c r="AC693">
-        <v>-3238.26</v>
-      </c>
       <c r="AD693">
-        <v>-3238.26</v>
+        <v>-6476.52</v>
       </c>
       <c r="AE693">
         <v>-3238.26</v>
@@ -31765,7 +31666,7 @@
       <c r="E694">
         <v>-10343.67</v>
       </c>
-      <c r="AC694">
+      <c r="AD694">
         <v>-10343.67</v>
       </c>
     </row>
@@ -31785,14 +31686,8 @@
       <c r="E695">
         <v>-40622.52</v>
       </c>
-      <c r="AB695">
-        <v>-3385.21</v>
-      </c>
-      <c r="AC695">
-        <v>-3385.21</v>
-      </c>
       <c r="AD695">
-        <v>-3385.21</v>
+        <v>-10155.63</v>
       </c>
       <c r="AE695">
         <v>-3385.21</v>
@@ -33430,7 +33325,7 @@
       <c r="E727">
         <v>-20674.89</v>
       </c>
-      <c r="AC727">
+      <c r="AE727">
         <v>-20674.89</v>
       </c>
     </row>
@@ -35462,14 +35357,8 @@
       <c r="E771">
         <v>-27438.84</v>
       </c>
-      <c r="AD771">
-        <v>-2286.57</v>
-      </c>
-      <c r="AE771">
-        <v>-2286.57</v>
-      </c>
       <c r="AF771">
-        <v>-2286.57</v>
+        <v>-6859.71</v>
       </c>
       <c r="AG771">
         <v>-2286.57</v>
@@ -35515,14 +35404,8 @@
       <c r="E772">
         <v>-1893.6</v>
       </c>
-      <c r="AD772">
-        <v>-210.4</v>
-      </c>
-      <c r="AE772">
-        <v>-210.4</v>
-      </c>
       <c r="AF772">
-        <v>-210.4</v>
+        <v>-631.2</v>
       </c>
       <c r="AG772">
         <v>-210.4</v>
@@ -35559,14 +35442,8 @@
       <c r="E773">
         <v>-13687.56</v>
       </c>
-      <c r="AD773">
-        <v>-1140.63</v>
-      </c>
-      <c r="AE773">
-        <v>-1140.63</v>
-      </c>
       <c r="AF773">
-        <v>-1140.63</v>
+        <v>-3421.89</v>
       </c>
       <c r="AG773">
         <v>-1140.63</v>
@@ -37619,11 +37496,8 @@
       <c r="E816">
         <v>-19847.04</v>
       </c>
-      <c r="AF816">
-        <v>-1653.92</v>
-      </c>
       <c r="AG816">
-        <v>-1653.92</v>
+        <v>-3307.84</v>
       </c>
       <c r="AH816">
         <v>-1653.92</v>
@@ -37672,7 +37546,7 @@
       <c r="E817">
         <v>-16084.93</v>
       </c>
-      <c r="AE817">
+      <c r="AG817">
         <v>-16084.93</v>
       </c>
     </row>
@@ -37692,14 +37566,8 @@
       <c r="E818">
         <v>-42144.6</v>
       </c>
-      <c r="AE818">
-        <v>-3512.05</v>
-      </c>
-      <c r="AF818">
-        <v>-3512.05</v>
-      </c>
       <c r="AG818">
-        <v>-3512.05</v>
+        <v>-10536.15</v>
       </c>
       <c r="AH818">
         <v>-3512.05</v>
@@ -39509,7 +39377,7 @@
       <c r="E858">
         <v>-5473.99</v>
       </c>
-      <c r="AG858">
+      <c r="AH858">
         <v>-5473.99</v>
       </c>
     </row>
@@ -41829,11 +41697,8 @@
       <c r="E908">
         <v>-4497.12</v>
       </c>
-      <c r="AH908">
-        <v>-374.76</v>
-      </c>
       <c r="AI908">
-        <v>-374.76</v>
+        <v>-749.52</v>
       </c>
       <c r="AJ908">
         <v>-374.76</v>
@@ -45024,7 +44889,7 @@
       <c r="E980">
         <v>-17481.73</v>
       </c>
-      <c r="AI980">
+      <c r="AK980">
         <v>-17481.73</v>
       </c>
     </row>
@@ -45044,11 +44909,8 @@
       <c r="E981">
         <v>-24450.84</v>
       </c>
-      <c r="AJ981">
-        <v>-2037.57</v>
-      </c>
       <c r="AK981">
-        <v>-2037.57</v>
+        <v>-4075.14</v>
       </c>
       <c r="AL981">
         <v>-2037.57</v>
@@ -47235,14 +47097,8 @@
       <c r="E1028">
         <v>-38091.35</v>
       </c>
-      <c r="AJ1028">
-        <v>-3462.85</v>
-      </c>
-      <c r="AK1028">
-        <v>-3462.85</v>
-      </c>
       <c r="AL1028">
-        <v>-3462.85</v>
+        <v>-10388.55</v>
       </c>
       <c r="AM1028">
         <v>-3462.85</v>
@@ -49454,11 +49310,8 @@
       <c r="E1080">
         <v>-3341.64</v>
       </c>
-      <c r="AL1080">
-        <v>-278.47</v>
-      </c>
       <c r="AM1080">
-        <v>-278.47</v>
+        <v>-556.94</v>
       </c>
       <c r="AN1080">
         <v>-278.47</v>
@@ -49551,7 +49404,7 @@
       <c r="E1082">
         <v>-20176.88</v>
       </c>
-      <c r="AK1082">
+      <c r="AM1082">
         <v>-20176.88</v>
       </c>
     </row>
@@ -49571,14 +49424,8 @@
       <c r="E1083">
         <v>-46251.36</v>
       </c>
-      <c r="AK1083">
-        <v>-3854.28</v>
-      </c>
-      <c r="AL1083">
-        <v>-3854.28</v>
-      </c>
       <c r="AM1083">
-        <v>-3854.28</v>
+        <v>-11562.84</v>
       </c>
       <c r="AN1083">
         <v>-3854.28</v>
@@ -49677,14 +49524,8 @@
       <c r="E1085">
         <v>-18183.48</v>
       </c>
-      <c r="AK1085">
-        <v>-1515.29</v>
-      </c>
-      <c r="AL1085">
-        <v>-1515.29</v>
-      </c>
       <c r="AM1085">
-        <v>-1515.29</v>
+        <v>-4545.87</v>
       </c>
       <c r="AN1085">
         <v>-1515.29</v>
@@ -49759,11 +49600,8 @@
       <c r="E1087">
         <v>-27298.44</v>
       </c>
-      <c r="AL1087">
-        <v>-2274.87</v>
-      </c>
       <c r="AM1087">
-        <v>-2274.87</v>
+        <v>-4549.74</v>
       </c>
       <c r="AN1087">
         <v>-2274.87</v>
